--- a/astro-site/public/dl/guia-churreria-chocolateria/plan-financiero-3-anos-churreria.xlsx
+++ b/astro-site/public/dl/guia-churreria-chocolateria/plan-financiero-3-anos-churreria.xlsx
@@ -1110,19 +1110,19 @@
       </c>
       <c r="E6" s="29">
         <f>'0. Supuestos'!$B$11</f>
-        <v>0.2731486410667722</v>
+        <v>0.2731486410667721</v>
       </c>
       <c r="F6" s="29">
         <f>D6-E6</f>
-        <v>1.874903306985176</v>
+        <v>1.8749033069851762</v>
       </c>
       <c r="G6" s="25">
         <f>C6*F6</f>
-        <v>128621.6479399703</v>
+        <v>128621.64793997031</v>
       </c>
       <c r="H6" s="23">
         <f>IFERROR(G6/$G$12,"")</f>
-        <v>0.6482343162769347</v>
+        <v>0.6482343162769348</v>
       </c>
     </row>
     <row r="7">
@@ -1141,23 +1141,23 @@
       </c>
       <c r="D7" s="29">
         <f>'0. Supuestos'!$B$14</f>
-        <v>2.192424242424243</v>
+        <v>2.192424242424242</v>
       </c>
       <c r="E7" s="29">
         <f>'0. Supuestos'!$B$12</f>
-        <v>0.3054629283128055</v>
+        <v>0.3054629283128054</v>
       </c>
       <c r="F7" s="29">
         <f>D7-E7</f>
-        <v>1.8869613141114372</v>
+        <v>1.8869613141114365</v>
       </c>
       <c r="G7" s="25">
         <f>C7*F7</f>
-        <v>55478.07785586184</v>
+        <v>55478.077855861826</v>
       </c>
       <c r="H7" s="23">
         <f>IFERROR(G7/$G$12,"")</f>
-        <v>0.2796014080307659</v>
+        <v>0.27960140803076583</v>
       </c>
     </row>
     <row r="8">
@@ -1176,15 +1176,15 @@
       </c>
       <c r="D8" s="44">
         <f>B6*D6+B7*D7</f>
-        <v>2.1613636363636366</v>
+        <v>2.161363636363636</v>
       </c>
       <c r="E8" s="44">
         <f>B6*E6+B7*E7</f>
-        <v>0.28284292724058224</v>
+        <v>0.28284292724058213</v>
       </c>
       <c r="F8" s="44">
         <f>D8-E8</f>
-        <v>1.8785207091230545</v>
+        <v>1.878520709123054</v>
       </c>
       <c r="G8" s="21">
         <f>G6+G7</f>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B15" s="32">
         <f>'PyG 3 Años'!$C$22</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
@@ -1305,11 +1305,11 @@
       </c>
       <c r="B17" s="25">
         <f>G6</f>
-        <v>128621.6479399703</v>
+        <v>128621.64793997031</v>
       </c>
       <c r="C17" s="32">
         <f>B17-$B$15</f>
-        <v>-37658.04692375324</v>
+        <v>-37658.04692375325</v>
       </c>
       <c r="D17" t="str">
         <f>IF(NOT(ISNUMBER(C17)),"",IF(C17&gt;=0,"Paga los fijos","No llega a los fijos"))</f>
@@ -1328,11 +1328,11 @@
       </c>
       <c r="B18" s="25">
         <f>G7</f>
-        <v>55478.07785586184</v>
+        <v>55478.077855861826</v>
       </c>
       <c r="C18" s="32">
         <f>B18-$B$15</f>
-        <v>-110801.6170078617</v>
+        <v>-110801.61700786173</v>
       </c>
       <c r="D18" t="str">
         <f>IF(NOT(ISNUMBER(C18)),"",IF(C18&gt;=0,"Paga los fijos","No llega a los fijos"))</f>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E18" s="31">
         <f>IFERROR(IF(F7-'0. Supuestos'!$B$17&lt;=0,"",$B$15/(F7-'0. Supuestos'!$B$17)/'Punto de Equilibrio'!$B$10),"")</f>
-        <v>248.51891282002305</v>
+        <v>248.51891282002316</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C19" s="32">
         <f>B19-$B$15</f>
-        <v>17820.03093210861</v>
+        <v>17820.03093210858</v>
       </c>
       <c r="D19" t="str">
         <f>IF(NOT(ISNUMBER(C19)),"",IF(C19&gt;=0,"Paga los fijos","No llega a los fijos"))</f>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E19" s="31">
         <f>IFERROR(IF(F8-'0. Supuestos'!$B$17&lt;=0,"",$B$15/(F8-'0. Supuestos'!$B$17)/'Punto de Equilibrio'!$B$10),"")</f>
-        <v>249.65270269727364</v>
+        <v>249.6527026972737</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C20" s="32">
         <f>B20-$B$15</f>
-        <v>32138.754623330984</v>
+        <v>32138.754623330955</v>
       </c>
       <c r="D20" t="str">
         <f>IF(NOT(ISNUMBER(C20)),"",IF(C20&gt;=0,"Paga los fijos","No llega a los fijos"))</f>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E20" s="31">
         <f>'Punto de Equilibrio'!$B$12</f>
-        <v>250.01090252739175</v>
+        <v>250.0109025273918</v>
       </c>
     </row>
     <row r="21">
@@ -1411,8 +1411,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A23:H23"/>
   </mergeCells>
   <conditionalFormatting sqref="C17">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>86415.65000000001</v>
+        <v>86415.64999999999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>4668.300000000003</v>
+        <v>4668.299999999988</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.2731486410667722</v>
+        <v>0.2731486410667721</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>0.3054629283128055</v>
+        <v>0.3054629283128054</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>2.192424242424243</v>
+        <v>2.192424242424242</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>2106.453743784074</v>
+        <v>2106.453743784075</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="B95" s="11" t="n">
-        <v>86415.65000000001</v>
+        <v>86415.64999999999</v>
       </c>
       <c r="C95" s="23">
         <f>IFERROR(IF(B95=0,ABS('0. Supuestos'!$B$7-B95),ABS('0. Supuestos'!$B$7-B95)/ABS(B95)),"")</f>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>0.2731486410667722</v>
+        <v>0.2731486410667721</v>
       </c>
       <c r="C96" s="23">
         <f>IFERROR(IF(B96=0,ABS('0. Supuestos'!$B$11-B96),ABS('0. Supuestos'!$B$11-B96)/ABS(B96)),"")</f>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>0.3054629283128055</v>
+        <v>0.3054629283128054</v>
       </c>
       <c r="C97" s="23">
         <f>IFERROR(IF(B97=0,ABS('0. Supuestos'!$B$12-B97),ABS('0. Supuestos'!$B$12-B97)/ABS(B97)),"")</f>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>2.192424242424243</v>
+        <v>2.192424242424242</v>
       </c>
       <c r="C99" s="23">
         <f>IFERROR(IF(B99=0,ABS('0. Supuestos'!$B$14-B99),ABS('0. Supuestos'!$B$14-B99)/ABS(B99)),"")</f>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="B119" s="11" t="n">
-        <v>4668.300000000003</v>
+        <v>4668.299999999988</v>
       </c>
       <c r="C119" s="23">
         <f>IFERROR(IF(B119=0,ABS('0. Supuestos'!$B$9-B119),ABS('0. Supuestos'!$B$9-B119)/ABS(B119)),"")</f>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="B122" s="11" t="n">
-        <v>2106.453743784074</v>
+        <v>2106.453743784075</v>
       </c>
       <c r="C122" s="23">
         <f>IFERROR(IF(B122=0,ABS('0. Supuestos'!$B$36-B122),ABS('0. Supuestos'!$B$36-B122)/ABS(B122)),"")</f>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="B6" s="25">
         <f>'0. Supuestos'!$B$7</f>
-        <v>86415.65000000001</v>
+        <v>86415.65</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="B7" s="25">
         <f>'0. Supuestos'!$B$9</f>
-        <v>4668.300000000003</v>
+        <v>4668.299999999988</v>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B16" s="25">
         <f>IFERROR(INDEX('Financiación'!$B$117:$B$123,'0. Supuestos'!$B$55)/'0. Supuestos'!$B$44,"")</f>
-        <v>449.56322917604666</v>
+        <v>449.5632291760467</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="B22" s="25">
         <f>B6</f>
-        <v>86415.65000000001</v>
+        <v>86415.65</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -4987,15 +4987,15 @@
       </c>
       <c r="B9" s="25">
         <f>'Tesorería 12 meses'!$N$13</f>
-        <v>182135.35789772728</v>
+        <v>182135.35789772726</v>
       </c>
       <c r="C9" s="25">
         <f>C8*'Canales y Punto Muerto'!$D$8</f>
-        <v>211819.0397727273</v>
+        <v>211819.03977272726</v>
       </c>
       <c r="D9" s="25">
         <f>D8*'Canales y Punto Muerto'!$D$8</f>
-        <v>211819.0397727273</v>
+        <v>211819.03977272726</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -5011,15 +5011,15 @@
       </c>
       <c r="B10" s="25">
         <f>'Tesorería 12 meses'!$N$15</f>
-        <v>23834.812853831638</v>
+        <v>23834.812853831623</v>
       </c>
       <c r="C10" s="25">
         <f>C8*'Canales y Punto Muerto'!$E$8</f>
-        <v>27719.313976895162</v>
+        <v>27719.31397689515</v>
       </c>
       <c r="D10" s="25">
         <f>D8*'Canales y Punto Muerto'!$E$8</f>
-        <v>27719.313976895162</v>
+        <v>27719.31397689515</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -5035,15 +5035,15 @@
       </c>
       <c r="B11" s="25">
         <f>B9-B10</f>
-        <v>158300.54504389566</v>
+        <v>158300.54504389563</v>
       </c>
       <c r="C11" s="25">
         <f>C9-C10</f>
-        <v>184099.72579583214</v>
+        <v>184099.7257958321</v>
       </c>
       <c r="D11" s="25">
         <f>D9-D10</f>
-        <v>184099.72579583214</v>
+        <v>184099.7257958321</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -5121,15 +5121,15 @@
       </c>
       <c r="B15" s="21">
         <f>B11+B12-B13+B14</f>
-        <v>173009.28561377656</v>
+        <v>173009.28561377653</v>
       </c>
       <c r="C15" s="21">
         <f>C11+C12-C13+C14</f>
-        <v>198418.44948705452</v>
+        <v>198418.4494870545</v>
       </c>
       <c r="D15" s="21">
         <f>D11+D12-D13+D14</f>
-        <v>198418.44948705452</v>
+        <v>198418.4494870545</v>
       </c>
     </row>
     <row r="16">
@@ -5238,15 +5238,15 @@
       </c>
       <c r="B21" s="25">
         <f>'Financiación'!$B$117</f>
-        <v>6075.678474934056</v>
+        <v>6075.678474934055</v>
       </c>
       <c r="C21" s="25">
         <f>'Financiación'!$B$118</f>
-        <v>5394.75875011256</v>
+        <v>5394.758750112561</v>
       </c>
       <c r="D21" s="25">
         <f>'Financiación'!$B$119</f>
-        <v>4552.342042557509</v>
+        <v>4552.34204255751</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -5262,11 +5262,11 @@
       </c>
       <c r="B22" s="21">
         <f>SUM(B17:B21)</f>
-        <v>166960.61458854502</v>
+        <v>166960.61458854505</v>
       </c>
       <c r="C22" s="21">
         <f>SUM(C17:C21)</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
       <c r="D22" s="21">
         <f>SUM(D17:D21)</f>
@@ -5281,15 +5281,15 @@
       </c>
       <c r="B23" s="21">
         <f>B15-B22</f>
-        <v>6048.671025231539</v>
+        <v>6048.671025231481</v>
       </c>
       <c r="C23" s="21">
         <f>C15-C22</f>
-        <v>32138.754623330984</v>
+        <v>32138.754623330926</v>
       </c>
       <c r="D23" s="21">
         <f>D15-D22</f>
-        <v>32981.17133088602</v>
+        <v>32981.17133088599</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -5356,15 +5356,15 @@
       </c>
       <c r="B28" s="21">
         <f>B9+B27</f>
-        <v>202873.07744318183</v>
+        <v>202873.0774431818</v>
       </c>
       <c r="C28" s="21">
         <f>C9+C27</f>
-        <v>232556.75931818184</v>
+        <v>232556.7593181818</v>
       </c>
       <c r="D28" s="21">
         <f>D9+D27</f>
-        <v>232556.75931818184</v>
+        <v>232556.7593181818</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
@@ -5375,15 +5375,15 @@
       </c>
       <c r="B29" s="23">
         <f>IFERROR(B23/B28,"")</f>
-        <v>0.029815050382550515</v>
+        <v>0.029815050382550234</v>
       </c>
       <c r="C29" s="23">
         <f>IFERROR(C23/C28,"")</f>
-        <v>0.13819746507285588</v>
+        <v>0.13819746507285563</v>
       </c>
       <c r="D29" s="23">
         <f>IFERROR(D23/D28,"")</f>
-        <v>0.14181987841411872</v>
+        <v>0.1418198784141186</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -5399,15 +5399,15 @@
       </c>
       <c r="B30" s="29">
         <f>IFERROR(B15/B7,"")</f>
-        <v>1.8470829331893812</v>
+        <v>1.847082933189381</v>
       </c>
       <c r="C30" s="29">
         <f>IFERROR(C15/C7,"")</f>
-        <v>1.8474715967137292</v>
+        <v>1.847471596713729</v>
       </c>
       <c r="D30" s="29">
         <f>IFERROR(D15/D7,"")</f>
-        <v>1.8474715967137292</v>
+        <v>1.847471596713729</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -5418,15 +5418,15 @@
       </c>
       <c r="B31" s="29">
         <f>IFERROR(B23/B7,"")</f>
-        <v>0.06457686348768234</v>
+        <v>0.06457686348768171</v>
       </c>
       <c r="C31" s="29">
         <f>IFERROR(C23/C7,"")</f>
-        <v>0.2992435253568993</v>
+        <v>0.29924352535689874</v>
       </c>
       <c r="D31" s="29">
         <f>IFERROR(D23/D7,"")</f>
-        <v>0.30708725633972084</v>
+        <v>0.30708725633972056</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -5437,15 +5437,15 @@
       </c>
       <c r="B32" s="25">
         <f>B23+B20+B21</f>
-        <v>20299.084500165594</v>
+        <v>20299.084500165536</v>
       </c>
       <c r="C32" s="25">
         <f>C23+C20+C21</f>
-        <v>45708.248373443545</v>
+        <v>45708.248373443486</v>
       </c>
       <c r="D32" s="25">
         <f>D23+D20+D21</f>
-        <v>45708.24837344353</v>
+        <v>45708.2483734435</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -5464,8 +5464,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A34:E34"/>
   </mergeCells>
   <conditionalFormatting sqref="B23:D23">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="B6" s="25">
         <f>'PyG 3 Años'!$C$22</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="B7" s="25">
         <f>'PyG 3 Años'!$C$15</f>
-        <v>198418.44948705452</v>
+        <v>198418.4494870545</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B9" s="29">
         <f>IFERROR(B7/B8,"")</f>
-        <v>1.8474715967137292</v>
+        <v>1.847471596713729</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="B11" s="26">
         <f>IFERROR(B6/B9,"")</f>
-        <v>90003.92490986103</v>
+        <v>90003.92490986105</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="B12" s="30">
         <f>IFERROR(B11/B10,"")</f>
-        <v>250.01090252739175</v>
+        <v>250.0109025273918</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B14" s="31">
         <f>B13-B12</f>
-        <v>48.322430805941565</v>
+        <v>48.32243080594151</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="B15" s="32">
         <f>B7-B6</f>
-        <v>32138.754623330984</v>
+        <v>32138.754623330926</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B17" s="25">
         <f>IFERROR(B6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B18" s="25">
         <f>IFERROR(B11/'0. Supuestos'!$B$44*'PyG 3 Años'!$C$28/'PyG 3 Años'!$C$7,"")</f>
-        <v>16240.705387146387</v>
+        <v>16240.705387146389</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
@@ -5794,15 +5794,15 @@
       </c>
       <c r="F23" s="25">
         <f>IFERROR(IF(OR(B23='0. Supuestos'!$B$46,B23='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C23/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D23*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D23*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>20698.24362437108</v>
+        <v>20698.243624371076</v>
       </c>
       <c r="G23" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H23" s="32">
         <f>F23-G23</f>
-        <v>6841.602385727452</v>
+        <v>6841.602385727447</v>
       </c>
       <c r="I23" t="str">
         <f>IF(NOT(ISNUMBER(H23)),"",IF(H23&gt;=0,"Sí","No"))</f>
@@ -5832,15 +5832,15 @@
       </c>
       <c r="F24" s="25">
         <f>IFERROR(IF(OR(B24='0. Supuestos'!$B$46,B24='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C24/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D24*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D24*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>19042.384134421394</v>
+        <v>19042.384134421387</v>
       </c>
       <c r="G24" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H24" s="32">
         <f>F24-G24</f>
-        <v>5185.7428957777665</v>
+        <v>5185.742895777757</v>
       </c>
       <c r="I24" t="str">
         <f>IF(NOT(ISNUMBER(H24)),"",IF(H24&gt;=0,"Sí","No"))</f>
@@ -5870,15 +5870,15 @@
       </c>
       <c r="F25" s="25">
         <f>IFERROR(IF(OR(B25='0. Supuestos'!$B$46,B25='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C25/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D25*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D25*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>18214.454389446553</v>
+        <v>18214.45438944655</v>
       </c>
       <c r="G25" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H25" s="32">
         <f>F25-G25</f>
-        <v>4357.8131508029255</v>
+        <v>4357.81315080292</v>
       </c>
       <c r="I25" t="str">
         <f>IF(NOT(ISNUMBER(H25)),"",IF(H25&gt;=0,"Sí","No"))</f>
@@ -5908,15 +5908,15 @@
       </c>
       <c r="F26" s="25">
         <f>IFERROR(IF(OR(B26='0. Supuestos'!$B$46,B26='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C26/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D26*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D26*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>15730.665154522023</v>
+        <v>15730.66515452202</v>
       </c>
       <c r="G26" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H26" s="32">
         <f>F26-G26</f>
-        <v>1874.0239158783952</v>
+        <v>1874.0239158783897</v>
       </c>
       <c r="I26" t="str">
         <f>IF(NOT(ISNUMBER(H26)),"",IF(H26&gt;=0,"Sí","No"))</f>
@@ -5946,15 +5946,15 @@
       </c>
       <c r="F27" s="25">
         <f>IFERROR(IF(OR(B27='0. Supuestos'!$B$46,B27='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C27/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D27*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D27*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>14074.805664572335</v>
+        <v>14074.805664572332</v>
       </c>
       <c r="G27" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H27" s="32">
         <f>F27-G27</f>
-        <v>218.16442592870771</v>
+        <v>218.16442592870226</v>
       </c>
       <c r="I27" t="str">
         <f>IF(NOT(ISNUMBER(H27)),"",IF(H27&gt;=0,"Sí","No"))</f>
@@ -5984,15 +5984,15 @@
       </c>
       <c r="F28" s="25">
         <f>IFERROR(IF(OR(B28='0. Supuestos'!$B$46,B28='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C28/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D28*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D28*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>11591.016429647805</v>
+        <v>11591.016429647803</v>
       </c>
       <c r="G28" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H28" s="32">
         <f>F28-G28</f>
-        <v>-2265.6248089958226</v>
+        <v>-2265.6248089958262</v>
       </c>
       <c r="I28" t="str">
         <f>IF(NOT(ISNUMBER(H28)),"",IF(H28&gt;=0,"Sí","No"))</f>
@@ -6026,11 +6026,11 @@
       </c>
       <c r="G29" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H29" s="32">
         <f>F29-G29</f>
-        <v>-4898.537014205434</v>
+        <v>-4898.537014205436</v>
       </c>
       <c r="I29" t="str">
         <f>IF(NOT(ISNUMBER(H29)),"",IF(H29&gt;=0,"Sí","No"))</f>
@@ -6064,11 +6064,11 @@
       </c>
       <c r="G30" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H30" s="32">
         <f>F30-G30</f>
-        <v>-5712.910125517998</v>
+        <v>-5712.910125517999</v>
       </c>
       <c r="I30" t="str">
         <f>IF(NOT(ISNUMBER(H30)),"",IF(H30&gt;=0,"Sí","No"))</f>
@@ -6098,15 +6098,15 @@
       </c>
       <c r="F31" s="25">
         <f>IFERROR(IF(OR(B31='0. Supuestos'!$B$46,B31='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C31/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D31*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D31*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>13246.875919597493</v>
+        <v>13246.875919597489</v>
       </c>
       <c r="G31" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H31" s="32">
         <f>F31-G31</f>
-        <v>-609.7653190461351</v>
+        <v>-609.7653190461406</v>
       </c>
       <c r="I31" t="str">
         <f>IF(NOT(ISNUMBER(H31)),"",IF(H31&gt;=0,"Sí","No"))</f>
@@ -6136,15 +6136,15 @@
       </c>
       <c r="F32" s="25">
         <f>IFERROR(IF(OR(B32='0. Supuestos'!$B$46,B32='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C32/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D32*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D32*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>18214.454389446553</v>
+        <v>18214.45438944655</v>
       </c>
       <c r="G32" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H32" s="32">
         <f>F32-G32</f>
-        <v>4357.8131508029255</v>
+        <v>4357.81315080292</v>
       </c>
       <c r="I32" t="str">
         <f>IF(NOT(ISNUMBER(H32)),"",IF(H32&gt;=0,"Sí","No"))</f>
@@ -6174,15 +6174,15 @@
       </c>
       <c r="F33" s="25">
         <f>IFERROR(IF(OR(B33='0. Supuestos'!$B$46,B33='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C33/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D33*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D33*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>21526.173369345925</v>
+        <v>21526.17336934592</v>
       </c>
       <c r="G33" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H33" s="32">
         <f>F33-G33</f>
-        <v>7669.532130702297</v>
+        <v>7669.532130702291</v>
       </c>
       <c r="I33" t="str">
         <f>IF(NOT(ISNUMBER(H33)),"",IF(H33&gt;=0,"Sí","No"))</f>
@@ -6212,15 +6212,15 @@
       </c>
       <c r="F34" s="25">
         <f>IFERROR(IF(OR(B34='0. Supuestos'!$B$46,B34='0. Supuestos'!$B$47),IF(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)&gt;0,'0. Supuestos'!$B$33*C34/(INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$46)+INDEX('0. Supuestos'!$B$20:$B$31,'0. Supuestos'!$B$47)),0),D34*('Canales y Punto Muerto'!$D$8-'Canales y Punto Muerto'!$E$8))-D34*'0. Supuestos'!$B$17+'0. Supuestos'!$B$32/'0. Supuestos'!$B$44,"")</f>
-        <v>28977.541074119516</v>
+        <v>28977.54107411951</v>
       </c>
       <c r="G34" s="25">
         <f>IFERROR($B$6/'0. Supuestos'!$B$44,"")</f>
-        <v>13856.641238643628</v>
+        <v>13856.64123864363</v>
       </c>
       <c r="H34" s="32">
         <f>F34-G34</f>
-        <v>15120.899835475888</v>
+        <v>15120.899835475879</v>
       </c>
       <c r="I34" t="str">
         <f>IF(NOT(ISNUMBER(H34)),"",IF(H34&gt;=0,"Sí","No"))</f>
@@ -6242,15 +6242,15 @@
       <c r="E35" s="34" t="n"/>
       <c r="F35" s="21">
         <f>SUM(F23:F34)</f>
-        <v>198418.4494870545</v>
+        <v>198418.44948705446</v>
       </c>
       <c r="G35" s="21">
         <f>SUM(G23:G34)</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
       <c r="H35" s="21">
         <f>SUM(H23:H34)</f>
-        <v>32138.75462333097</v>
+        <v>32138.754623330904</v>
       </c>
       <c r="I35" s="34" t="n"/>
     </row>
@@ -6438,15 +6438,15 @@
       </c>
       <c r="B8" s="25">
         <f>('PyG 3 Años'!$C$15-'PyG 3 Años'!$C$14)*(1+B6)</f>
-        <v>168655.68206399633</v>
+        <v>168655.6820639963</v>
       </c>
       <c r="C8" s="25">
         <f>('PyG 3 Años'!$C$15-'PyG 3 Años'!$C$14)*(1+C6)</f>
-        <v>198418.44948705452</v>
+        <v>198418.4494870545</v>
       </c>
       <c r="D8" s="25">
         <f>('PyG 3 Años'!$C$15-'PyG 3 Años'!$C$14)*(1+D6)</f>
-        <v>218260.29443575998</v>
+        <v>218260.29443575995</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -6463,15 +6463,15 @@
       </c>
       <c r="B10" s="21">
         <f>B8+B24</f>
-        <v>170762.1358077804</v>
+        <v>170762.13580778037</v>
       </c>
       <c r="C10" s="21">
         <f>C8+C24</f>
-        <v>226131.73196434177</v>
+        <v>226131.73196434174</v>
       </c>
       <c r="D10" s="21">
         <f>D8+D24</f>
-        <v>192653.4657022568</v>
+        <v>192653.46570225677</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -6482,15 +6482,15 @@
       </c>
       <c r="B11" s="25">
         <f>'PyG 3 Años'!$C$22</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
       <c r="C11" s="25">
         <f>'PyG 3 Años'!$C$22</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
       <c r="D11" s="25">
         <f>'PyG 3 Años'!$C$22</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6506,15 +6506,15 @@
       </c>
       <c r="B12" s="21">
         <f>B10-B11</f>
-        <v>4482.440944056871</v>
+        <v>4482.440944056812</v>
       </c>
       <c r="C12" s="21">
         <f>C10-C11</f>
-        <v>59852.03710061824</v>
+        <v>59852.03710061818</v>
       </c>
       <c r="D12" s="21">
         <f>D10-D11</f>
-        <v>26373.770838533266</v>
+        <v>26373.770838533208</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -6544,15 +6544,15 @@
       </c>
       <c r="B14" s="31">
         <f>IFERROR(IF(B10&lt;=0,"",B11/(B10/B7)/'Punto de Equilibrio'!$B$10),"")</f>
-        <v>246.92686753846147</v>
+        <v>246.92686753846158</v>
       </c>
       <c r="C14" s="31">
         <f>IFERROR(IF(C10&lt;=0,"",C11/(C10/C7)/'Punto de Equilibrio'!$B$10),"")</f>
-        <v>219.371139129499</v>
+        <v>219.37113912949903</v>
       </c>
       <c r="D14" s="31">
         <f>IFERROR(IF(D10&lt;=0,"",D11/(D10/D7)/'Punto de Equilibrio'!$B$10),"")</f>
-        <v>283.24148231058473</v>
+        <v>283.24148231058484</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -6582,15 +6582,15 @@
       </c>
       <c r="B16" s="31">
         <f>IFERROR(B15-B14,"")</f>
-        <v>6.6564657948718775</v>
+        <v>6.656465794871764</v>
       </c>
       <c r="C16" s="31">
         <f>IFERROR(C15-C14,"")</f>
-        <v>78.96219420383431</v>
+        <v>78.96219420383429</v>
       </c>
       <c r="D16" s="31">
         <f>IFERROR(D15-D14,"")</f>
-        <v>44.92518435608196</v>
+        <v>44.92518435608184</v>
       </c>
     </row>
     <row r="17"/>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B21" s="32">
         <f>IFERROR('PyG 3 Años'!$C$22*B20/'0. Supuestos'!$B$44,"")</f>
-        <v>27713.282477287255</v>
+        <v>27713.28247728726</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -6667,11 +6667,11 @@
       </c>
       <c r="C22" s="25">
         <f>$B$21</f>
-        <v>27713.282477287255</v>
+        <v>27713.28247728726</v>
       </c>
       <c r="D22" s="32">
         <f>B22-C22</f>
-        <v>-27713.282477287255</v>
+        <v>-27713.28247728726</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -6691,11 +6691,11 @@
       </c>
       <c r="C23" s="25">
         <f>$B$21</f>
-        <v>27713.282477287255</v>
+        <v>27713.28247728726</v>
       </c>
       <c r="D23" s="32">
         <f>B23-C23</f>
-        <v>-10344.573420211236</v>
+        <v>-10344.57342021124</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -6711,15 +6711,15 @@
       </c>
       <c r="B24" s="25">
         <f>'0. Supuestos'!$B$36</f>
-        <v>2106.453743784074</v>
+        <v>2106.453743784075</v>
       </c>
       <c r="C24" s="25">
         <f>$B$21</f>
-        <v>27713.282477287255</v>
+        <v>27713.28247728726</v>
       </c>
       <c r="D24" s="32">
         <f>B24-C24</f>
-        <v>-25606.828733503182</v>
+        <v>-25606.828733503186</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -6739,11 +6739,11 @@
       </c>
       <c r="C25" s="25">
         <f>$B$21</f>
-        <v>27713.282477287255</v>
+        <v>27713.28247728726</v>
       </c>
       <c r="D25" s="32">
         <f>B25-C25</f>
-        <v>-10344.573420211236</v>
+        <v>-10344.57342021124</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="C33" s="25">
         <f>'Canales y Punto Muerto'!$G$7</f>
-        <v>55478.07785586184</v>
+        <v>55478.077855861826</v>
       </c>
     </row>
     <row r="34">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C37" s="21">
         <f>C33+C34-C35+C36</f>
-        <v>59773.69496322855</v>
+        <v>59773.69496322853</v>
       </c>
     </row>
     <row r="38">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="B38" s="25">
         <f>'PyG 3 Años'!$C$22</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
       <c r="C38" s="25">
         <f>'PyG 3 Años'!$C$22-'0. Supuestos'!$B$88</f>
-        <v>166279.69486372353</v>
+        <v>166279.69486372356</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
@@ -6948,11 +6948,11 @@
       </c>
       <c r="B39" s="21">
         <f>B37-B38</f>
-        <v>32138.754623330984</v>
+        <v>32138.754623330955</v>
       </c>
       <c r="C39" s="21">
         <f>C37-C38</f>
-        <v>-106505.999900495</v>
+        <v>-106505.99990049502</v>
       </c>
     </row>
     <row r="40">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="C41" s="37">
         <f>MAX(0,C38-C37)</f>
-        <v>106505.999900495</v>
+        <v>106505.99990049502</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -6997,9 +6997,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:D12">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="B11" s="23">
         <f>IFERROR(B8/'PyG 3 Años'!$C$28,"")</f>
-        <v>0.5297210086465962</v>
+        <v>0.5297210086465963</v>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="B12" s="23">
         <f>IFERROR(B8/'PyG 3 Años'!$C$15,"")</f>
-        <v>0.6208606177100902</v>
+        <v>0.6208606177100903</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="B13" s="38">
         <f>IFERROR(B8/'Punto de Equilibrio'!$B$9/'Punto de Equilibrio'!$B$10,"")</f>
-        <v>185.22341761684356</v>
+        <v>185.22341761684362</v>
       </c>
     </row>
     <row r="14"/>
@@ -7214,8 +7214,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -7675,43 +7675,43 @@
       </c>
       <c r="B13" s="25">
         <f>IF(B9=1,0,B11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>8511.450000000003</v>
+        <v>8511.45</v>
       </c>
       <c r="C13" s="25">
         <f>IF(C9=1,0,C11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>13618.320000000003</v>
+        <v>13618.320000000002</v>
       </c>
       <c r="D13" s="25">
         <f>IF(D9=1,0,D11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>18357.650113636366</v>
+        <v>18357.65011363636</v>
       </c>
       <c r="E13" s="25">
         <f>IF(E9=1,0,E11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>27758.93352272728</v>
+        <v>27758.933522727275</v>
       </c>
       <c r="F13" s="25">
         <f>IF(F9=1,0,F11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>22004.032670454548</v>
+        <v>22004.032670454544</v>
       </c>
       <c r="G13" s="25">
         <f>IF(G9=1,0,G11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>22245.835227272724</v>
+        <v>22245.83522727272</v>
       </c>
       <c r="H13" s="25">
         <f>IF(H9=1,0,H11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>21278.625000000007</v>
+        <v>21278.625000000004</v>
       </c>
       <c r="I13" s="25">
         <f>IF(I9=1,0,I11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>18376.99431818182</v>
+        <v>18376.994318181816</v>
       </c>
       <c r="J13" s="25">
         <f>IF(J9=1,0,J11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>16442.573863636364</v>
+        <v>16442.57386363636</v>
       </c>
       <c r="K13" s="25">
         <f>IF(K9=1,0,K11*'Canales y Punto Muerto'!$D$8)</f>
-        <v>13540.943181818184</v>
+        <v>13540.94318181818</v>
       </c>
       <c r="L13" s="25">
         <f>IF(L9=1,0,L11*'Canales y Punto Muerto'!$D$8)</f>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="N13" s="37">
         <f>SUM(B13:M13)</f>
-        <v>182135.35789772728</v>
+        <v>182135.35789772726</v>
       </c>
     </row>
     <row r="14">
@@ -7793,43 +7793,43 @@
       </c>
       <c r="B15" s="25">
         <f>IF(B9=1,0,B11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>1113.835447473413</v>
+        <v>1113.8354474734126</v>
       </c>
       <c r="C15" s="25">
         <f>IF(C9=1,0,C11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>1782.1367159574609</v>
+        <v>1782.1367159574602</v>
       </c>
       <c r="D15" s="25">
         <f>IF(D9=1,0,D11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>2402.3405446642473</v>
+        <v>2402.340544664246</v>
       </c>
       <c r="E15" s="25">
         <f>IF(E9=1,0,E11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>3632.622425282608</v>
+        <v>3632.622425282607</v>
       </c>
       <c r="F15" s="25">
         <f>IF(F9=1,0,F11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>2879.5177761386526</v>
+        <v>2879.5177761386512</v>
       </c>
       <c r="G15" s="25">
         <f>IF(G9=1,0,G11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>2911.1608286236924</v>
+        <v>2911.160828623691</v>
       </c>
       <c r="H15" s="25">
         <f>IF(H9=1,0,H11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>2784.588618683533</v>
+        <v>2784.5886186835314</v>
       </c>
       <c r="I15" s="25">
         <f>IF(I9=1,0,I11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>2404.8719888630503</v>
+        <v>2404.8719888630494</v>
       </c>
       <c r="J15" s="25">
         <f>IF(J9=1,0,J11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>2151.7275689827293</v>
+        <v>2151.7275689827284</v>
       </c>
       <c r="K15" s="25">
         <f>IF(K9=1,0,K11*'Canales y Punto Muerto'!$E$8)</f>
-        <v>1772.0109391622477</v>
+        <v>1772.010939162247</v>
       </c>
       <c r="L15" s="25">
         <f>IF(L9=1,0,L11*'Canales y Punto Muerto'!$E$8)</f>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="N15" s="37">
         <f>SUM(B15:M15)</f>
-        <v>23834.812853831638</v>
+        <v>23834.812853831623</v>
       </c>
     </row>
     <row r="16">
@@ -7852,27 +7852,27 @@
       </c>
       <c r="B16" s="25">
         <f>B13-B15</f>
-        <v>7397.614552526589</v>
+        <v>7397.614552526588</v>
       </c>
       <c r="C16" s="25">
         <f>C13-C15</f>
-        <v>11836.183284042543</v>
+        <v>11836.183284042541</v>
       </c>
       <c r="D16" s="25">
         <f>D13-D15</f>
-        <v>15955.30956897212</v>
+        <v>15955.309568972112</v>
       </c>
       <c r="E16" s="25">
         <f>E13-E15</f>
-        <v>24126.31109744467</v>
+        <v>24126.311097444668</v>
       </c>
       <c r="F16" s="25">
         <f>F13-F15</f>
-        <v>19124.514894315897</v>
+        <v>19124.514894315893</v>
       </c>
       <c r="G16" s="25">
         <f>G13-G15</f>
-        <v>19334.674398649033</v>
+        <v>19334.67439864903</v>
       </c>
       <c r="H16" s="25">
         <f>H13-H15</f>
@@ -7880,15 +7880,15 @@
       </c>
       <c r="I16" s="25">
         <f>I13-I15</f>
-        <v>15972.122329318769</v>
+        <v>15972.122329318767</v>
       </c>
       <c r="J16" s="25">
         <f>J13-J15</f>
-        <v>14290.846294653635</v>
+        <v>14290.846294653631</v>
       </c>
       <c r="K16" s="25">
         <f>K13-K15</f>
-        <v>11768.932242655936</v>
+        <v>11768.932242655934</v>
       </c>
       <c r="L16" s="25">
         <f>L13-L15</f>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="N16" s="37">
         <f>SUM(B16:M16)</f>
-        <v>158300.54504389566</v>
+        <v>158300.54504389563</v>
       </c>
     </row>
     <row r="17">
@@ -8088,27 +8088,27 @@
       </c>
       <c r="B20" s="32">
         <f>B16+B17-B18+B19</f>
-        <v>7285.781755778622</v>
+        <v>7285.781755778621</v>
       </c>
       <c r="C20" s="32">
         <f>C16+C17-C18+C19</f>
-        <v>11657.250809245796</v>
+        <v>11657.250809245794</v>
       </c>
       <c r="D20" s="32">
         <f>D16+D17-D18+D19</f>
-        <v>15714.106559622525</v>
+        <v>15714.106559622518</v>
       </c>
       <c r="E20" s="32">
         <f>E16+E17-E18+E19</f>
-        <v>23761.583680778003</v>
+        <v>23761.583680778</v>
       </c>
       <c r="F20" s="32">
         <f>F16+F17-F18+F19</f>
-        <v>18835.401698177684</v>
+        <v>18835.40169817768</v>
       </c>
       <c r="G20" s="32">
         <f>G16+G17-G18+G19</f>
-        <v>19042.38413442139</v>
+        <v>19042.384134421387</v>
       </c>
       <c r="H20" s="32">
         <f>H16+H17-H18+H19</f>
@@ -8116,15 +8116,15 @@
       </c>
       <c r="I20" s="32">
         <f>I16+I17-I18+I19</f>
-        <v>15730.665154522021</v>
+        <v>15730.66515452202</v>
       </c>
       <c r="J20" s="32">
         <f>J16+J17-J18+J19</f>
-        <v>14074.805664572334</v>
+        <v>14074.80566457233</v>
       </c>
       <c r="K20" s="32">
         <f>K16+K17-K18+K19</f>
-        <v>11591.016429647805</v>
+        <v>11591.016429647803</v>
       </c>
       <c r="L20" s="32">
         <f>L16+L17-L18+L19</f>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="N20" s="37">
         <f>SUM(B20:M20)</f>
-        <v>173009.28561377656</v>
+        <v>173009.28561377653</v>
       </c>
     </row>
     <row r="21">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="N25" s="37">
         <f>SUM(B25:M25)</f>
-        <v>6075.678474934056</v>
+        <v>6075.678474934055</v>
       </c>
     </row>
     <row r="26">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="N27" s="37">
         <f>SUM(B27:M27)</f>
-        <v>165088.6652135624</v>
+        <v>165088.66521356243</v>
       </c>
     </row>
     <row r="28">
@@ -8508,27 +8508,27 @@
       </c>
       <c r="B28" s="32">
         <f>B20-B27</f>
-        <v>-5953.118337022293</v>
+        <v>-5953.118337022294</v>
       </c>
       <c r="C28" s="32">
         <f>C20-C27</f>
-        <v>-1581.6492835551198</v>
+        <v>-1581.6492835551217</v>
       </c>
       <c r="D28" s="32">
         <f>D20-D27</f>
-        <v>2475.20646682161</v>
+        <v>2475.2064668216026</v>
       </c>
       <c r="E28" s="32">
         <f>E20-E27</f>
-        <v>10522.683587977088</v>
+        <v>10522.683587977084</v>
       </c>
       <c r="F28" s="32">
         <f>F20-F27</f>
-        <v>5596.501605376769</v>
+        <v>5596.501605376765</v>
       </c>
       <c r="G28" s="32">
         <f>G20-G27</f>
-        <v>5803.484041620475</v>
+        <v>5803.4840416204715</v>
       </c>
       <c r="H28" s="32">
         <f>H20-H27</f>
@@ -8536,15 +8536,15 @@
       </c>
       <c r="I28" s="32">
         <f>I20-I27</f>
-        <v>1454.7877117291991</v>
+        <v>1454.7877117291973</v>
       </c>
       <c r="J28" s="32">
         <f>J20-J27</f>
-        <v>-201.07177822048834</v>
+        <v>-201.07177822049198</v>
       </c>
       <c r="K28" s="32">
         <f>K20-K27</f>
-        <v>-2684.861013145017</v>
+        <v>-2684.8610131450187</v>
       </c>
       <c r="L28" s="32">
         <f>L20-L27</f>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="N28" s="37">
         <f>SUM(B28:M28)</f>
-        <v>7920.620400214129</v>
+        <v>7920.620400214105</v>
       </c>
     </row>
     <row r="29">
@@ -8567,15 +8567,15 @@
       </c>
       <c r="B29" s="32">
         <f>$B$32+B28</f>
-        <v>73099.36159483946</v>
+        <v>73099.36159483947</v>
       </c>
       <c r="C29" s="32">
         <f>B29+C28</f>
-        <v>71517.71231128434</v>
+        <v>71517.71231128435</v>
       </c>
       <c r="D29" s="32">
         <f>C29+D28</f>
-        <v>73992.91877810594</v>
+        <v>73992.91877810596</v>
       </c>
       <c r="E29" s="32">
         <f>D29+E28</f>
@@ -8583,35 +8583,35 @@
       </c>
       <c r="F29" s="32">
         <f>E29+F28</f>
-        <v>90112.10397145982</v>
+        <v>90112.1039714598</v>
       </c>
       <c r="G29" s="32">
         <f>F29+G28</f>
-        <v>95915.5880130803</v>
+        <v>95915.58801308027</v>
       </c>
       <c r="H29" s="32">
         <f>G29+H28</f>
-        <v>99854.16495973403</v>
+        <v>99854.164959734</v>
       </c>
       <c r="I29" s="32">
         <f>H29+I28</f>
-        <v>101308.95267146322</v>
+        <v>101308.9526714632</v>
       </c>
       <c r="J29" s="32">
         <f>I29+J28</f>
-        <v>101107.88089324273</v>
+        <v>101107.8808932427</v>
       </c>
       <c r="K29" s="32">
         <f>J29+K28</f>
-        <v>98423.01988009772</v>
+        <v>98423.01988009768</v>
       </c>
       <c r="L29" s="32">
         <f>K29+L28</f>
-        <v>93105.24666174309</v>
+        <v>93105.24666174305</v>
       </c>
       <c r="M29" s="32">
         <f>L29+M28</f>
-        <v>86973.1003320759</v>
+        <v>86973.10033207586</v>
       </c>
     </row>
     <row r="30"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B32" s="32">
         <f>'Financiación'!$B$6+'Financiación'!$B$7-'0. Supuestos'!$B$7</f>
-        <v>79052.47993186176</v>
+        <v>79052.47993186177</v>
       </c>
     </row>
     <row r="33">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="B34" s="37">
         <f>MIN(B29:M29)</f>
-        <v>71517.71231128434</v>
+        <v>71517.71231128435</v>
       </c>
     </row>
     <row r="35">
@@ -8891,8 +8891,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
+    <mergeCell ref="A38:N38"/>
     <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A38:N38"/>
   </mergeCells>
   <conditionalFormatting sqref="B29:M29">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="B117" s="25">
         <f>SUM(C28:C39)</f>
-        <v>6075.678474934056</v>
+        <v>6075.678474934055</v>
       </c>
       <c r="C117" s="25">
         <f>SUM(D28:D39)</f>
@@ -11427,19 +11427,19 @@
       </c>
       <c r="D117" s="25">
         <f>B117+C117</f>
-        <v>12378.464099951438</v>
+        <v>12378.464099951436</v>
       </c>
       <c r="E117" s="25">
         <f>'PyG 3 Años'!B23+'PyG 3 Años'!B20+'PyG 3 Años'!B21</f>
-        <v>20299.084500165594</v>
+        <v>20299.084500165536</v>
       </c>
       <c r="F117" s="32">
         <f>E117-D117</f>
-        <v>7920.620400214157</v>
+        <v>7920.6204002141</v>
       </c>
       <c r="G117" s="33">
         <f>IFERROR(IF(D117=0,"",E117/D117),"")</f>
-        <v>1.6398710160047425</v>
+        <v>1.639871016004738</v>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
@@ -11453,27 +11453,27 @@
       </c>
       <c r="B118" s="25">
         <f>SUM(C40:C51)</f>
-        <v>5394.75875011256</v>
+        <v>5394.758750112561</v>
       </c>
       <c r="C118" s="25">
         <f>SUM(D40:D51)</f>
-        <v>13205.56944979031</v>
+        <v>13205.569449790311</v>
       </c>
       <c r="D118" s="25">
         <f>B118+C118</f>
-        <v>18600.32819990287</v>
+        <v>18600.328199902873</v>
       </c>
       <c r="E118" s="25">
         <f>'PyG 3 Años'!C23+'PyG 3 Años'!C20+'PyG 3 Años'!C21</f>
-        <v>45708.248373443545</v>
+        <v>45708.248373443486</v>
       </c>
       <c r="F118" s="32">
         <f>E118-D118</f>
-        <v>27107.920173540675</v>
+        <v>27107.920173540613</v>
       </c>
       <c r="G118" s="33">
         <f>IFERROR(IF(D118=0,"",E118/D118),"")</f>
-        <v>2.4573893472311004</v>
+        <v>2.457389347231097</v>
       </c>
     </row>
     <row r="119">
@@ -11482,27 +11482,27 @@
       </c>
       <c r="B119" s="25">
         <f>SUM(C52:C63)</f>
-        <v>4552.342042557509</v>
+        <v>4552.34204255751</v>
       </c>
       <c r="C119" s="25">
         <f>SUM(D52:D63)</f>
-        <v>14047.986157345364</v>
+        <v>14047.986157345362</v>
       </c>
       <c r="D119" s="25">
         <f>B119+C119</f>
-        <v>18600.328199902873</v>
+        <v>18600.32819990287</v>
       </c>
       <c r="E119" s="25">
         <f>'PyG 3 Años'!D23+'PyG 3 Años'!D20+'PyG 3 Años'!D21</f>
-        <v>45708.24837344353</v>
+        <v>45708.2483734435</v>
       </c>
       <c r="F119" s="32">
         <f>E119-D119</f>
-        <v>27107.920173540657</v>
+        <v>27107.92017354063</v>
       </c>
       <c r="G119" s="33">
         <f>IFERROR(IF(D119=0,"",E119/D119),"")</f>
-        <v>2.4573893472310995</v>
+        <v>2.457389347231098</v>
       </c>
     </row>
     <row r="120">
@@ -11523,15 +11523,15 @@
       </c>
       <c r="E120" s="25">
         <f>'PyG 3 Años'!D23+'PyG 3 Años'!D20+'PyG 3 Años'!D21</f>
-        <v>45708.24837344353</v>
+        <v>45708.2483734435</v>
       </c>
       <c r="F120" s="32">
         <f>E120-D120</f>
-        <v>27107.92017354066</v>
+        <v>27107.92017354063</v>
       </c>
       <c r="G120" s="33">
         <f>IFERROR(IF(D120=0,"",E120/D120),"")</f>
-        <v>2.4573893472311</v>
+        <v>2.457389347231098</v>
       </c>
     </row>
     <row r="121">
@@ -11540,27 +11540,27 @@
       </c>
       <c r="B121" s="25">
         <f>SUM(C76:C87)</f>
-        <v>2702.8607399960133</v>
+        <v>2702.860739996013</v>
       </c>
       <c r="C121" s="25">
         <f>SUM(D76:D87)</f>
-        <v>15897.467459906862</v>
+        <v>15897.467459906858</v>
       </c>
       <c r="D121" s="25">
         <f>B121+C121</f>
-        <v>18600.328199902877</v>
+        <v>18600.32819990287</v>
       </c>
       <c r="E121" s="25">
         <f>'PyG 3 Años'!D23+'PyG 3 Años'!D20+'PyG 3 Años'!D21</f>
-        <v>45708.24837344353</v>
+        <v>45708.2483734435</v>
       </c>
       <c r="F121" s="32">
         <f>E121-D121</f>
-        <v>27107.920173540653</v>
+        <v>27107.92017354063</v>
       </c>
       <c r="G121" s="33">
         <f>IFERROR(IF(D121=0,"",E121/D121),"")</f>
-        <v>2.457389347231099</v>
+        <v>2.457389347231098</v>
       </c>
     </row>
     <row r="122">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="B122" s="25">
         <f>SUM(C88:C99)</f>
-        <v>1688.7210433356047</v>
+        <v>1688.7210433356045</v>
       </c>
       <c r="C122" s="25">
         <f>SUM(D88:D99)</f>
@@ -11581,15 +11581,15 @@
       </c>
       <c r="E122" s="25">
         <f>'PyG 3 Años'!D23+'PyG 3 Años'!D20+'PyG 3 Años'!D21</f>
-        <v>45708.24837344353</v>
+        <v>45708.2483734435</v>
       </c>
       <c r="F122" s="32">
         <f>E122-D122</f>
-        <v>27107.920173540657</v>
+        <v>27107.920173540628</v>
       </c>
       <c r="G122" s="33">
         <f>IFERROR(IF(D122=0,"",E122/D122),"")</f>
-        <v>2.4573893472310995</v>
+        <v>2.4573893472310977</v>
       </c>
     </row>
     <row r="123">
@@ -11598,27 +11598,27 @@
       </c>
       <c r="B123" s="25">
         <f>SUM(C100:C111)</f>
-        <v>609.8868079421379</v>
+        <v>609.8868079421381</v>
       </c>
       <c r="C123" s="25">
         <f>SUM(D100:D111)</f>
-        <v>17990.441391960736</v>
+        <v>17990.441391960732</v>
       </c>
       <c r="D123" s="25">
         <f>B123+C123</f>
-        <v>18600.328199902873</v>
+        <v>18600.32819990287</v>
       </c>
       <c r="E123" s="25">
         <f>'PyG 3 Años'!D23+'PyG 3 Años'!D20+'PyG 3 Años'!D21</f>
-        <v>45708.24837344353</v>
+        <v>45708.2483734435</v>
       </c>
       <c r="F123" s="32">
         <f>E123-D123</f>
-        <v>27107.920173540657</v>
+        <v>27107.92017354063</v>
       </c>
       <c r="G123" s="33">
         <f>IFERROR(IF(D123=0,"",E123/D123),"")</f>
-        <v>2.4573893472310995</v>
+        <v>2.457389347231098</v>
       </c>
     </row>
     <row r="124">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="B124" s="37">
         <f>MIN(F117:F123)</f>
-        <v>7920.620400214157</v>
+        <v>7920.6204002141</v>
       </c>
     </row>
     <row r="125">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="B127" s="33">
         <f>IF(COUNT(G117:G123)=0,"",MIN(G117:G123))</f>
-        <v>1.6398710160047425</v>
+        <v>1.639871016004738</v>
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
@@ -11682,8 +11682,8 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A129:H129"/>
-    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="B16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
